--- a/livres_litt.xlsx
+++ b/livres_litt.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>Première phrase</t>
   </si>
@@ -137,6 +137,48 @@
   </si>
   <si>
     <t>La Bible - Anonyme</t>
+  </si>
+  <si>
+    <t>La première chose que je peux vous dire c’est qu’on habitait au sixième à pied et que Madame Rosa, avec tous ces kilos qu’elle portait sur elle et seulement deux jambes, c’était une vraie source de vie quotidienne, avec tous les soucis et les peines.</t>
+  </si>
+  <si>
+    <t>La vie devant soi - Romain Gary</t>
+  </si>
+  <si>
+    <t>Henri-Maximilien Ligure poursuivait par petites étapes sa route vers Paris.</t>
+  </si>
+  <si>
+    <t>L’Oeuvre au Noir - Marguerite Yourcenar</t>
+  </si>
+  <si>
+    <t>Mon cher Marc, je suis descendu ce matin chez-moi médecin Hermogène, qui vient de rentrer à la Villa après un assez long voyage en Asie.</t>
+  </si>
+  <si>
+    <t>Mémoires d’Hadrien - Marguerite Yourcenar</t>
+  </si>
+  <si>
+    <t>Ma bien-aimée, mon abandonnée, ma perdue, je t’ai laissée là-bas au fond du monde, j’ai regagné ma chambre d’homme de la ville avec ses meubles familiers sur lesquels j’ai si souvent posé mes mains qui les aimaient, avec ses livres qui m’ont nourri, avec mon vieux lit dede merisier où a dormi mon enfance et où, cette nuit, j’ai cherché en vain le sommeil.</t>
+  </si>
+  <si>
+    <t>La nuit des temps -  Barjavel</t>
+  </si>
+  <si>
+    <t>La sottise, l’erreur, le péché, la lésine, occupent nos esprits et travaillent nos corps, et nous alimentons nos aimables remords, comme les mendiants nourrissent leur vermine.</t>
+  </si>
+  <si>
+    <t>Les fleurs du mal - Baudelaire</t>
+  </si>
+  <si>
+    <t>Le perron au soleil. La sieste après déjeuner. Toby-Chien et Kiki-la-Doucette gisent sur la pierre brûlante.</t>
+  </si>
+  <si>
+    <t>Dialogues de Bêtes - Colette</t>
+  </si>
+  <si>
+    <t>Lorsque j’avais six ans j’ai vu, une fois, une magnifique image, dans un livre sur la Forêt Vierge qui s’appelait « Histoires Vécues ».</t>
+  </si>
+  <si>
+    <t>Le Petit Prince - Saint Exupéry</t>
   </si>
 </sst>
 </file>
@@ -184,13 +226,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="13"/>
+        <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
+        <fgColor indexed="13"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -304,19 +346,19 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,9 +533,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -573,7 +615,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -600,10 +642,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -850,9 +892,9 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -1130,7 +1172,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1157,10 +1199,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1402,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -1642,6 +1684,83 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" t="s" s="8">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" t="s" s="8">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s" s="8">
+        <v>45</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" t="s" s="8">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s" s="8">
+        <v>47</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" ht="66.85" customHeight="1">
+      <c r="A25" t="s" s="8">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s" s="8">
+        <v>49</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" ht="46.9" customHeight="1">
+      <c r="A26" t="s" s="8">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s" s="8">
+        <v>51</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" ht="40.35" customHeight="1">
+      <c r="A27" t="s" s="8">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s" s="8">
+        <v>53</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" ht="40.35" customHeight="1">
+      <c r="A28" t="s" s="8">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s" s="8">
+        <v>55</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
